--- a/roadmap_parallel.xlsx
+++ b/roadmap_parallel.xlsx
@@ -330,7 +330,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -368,9 +368,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1022,7 +1019,7 @@
       <c r="I7" s="11" t="n"/>
       <c r="J7" s="11" t="n"/>
       <c r="K7" s="11" t="n"/>
-      <c r="L7" s="11" t="n"/>
+      <c r="L7" s="12" t="n"/>
       <c r="M7" s="11" t="n"/>
       <c r="N7" s="11" t="n"/>
       <c r="O7" s="11" t="n"/>
@@ -1052,7 +1049,7 @@
       <c r="I8" s="11" t="n"/>
       <c r="J8" s="11" t="n"/>
       <c r="K8" s="11" t="n"/>
-      <c r="L8" s="11" t="n"/>
+      <c r="L8" s="12" t="n"/>
       <c r="M8" s="11" t="n"/>
       <c r="N8" s="11" t="n"/>
       <c r="O8" s="11" t="n"/>
@@ -1073,7 +1070,7 @@
       <c r="D9" s="11" t="n"/>
       <c r="E9" s="11" t="n"/>
       <c r="F9" s="11" t="n"/>
-      <c r="G9" s="19" t="inlineStr">
+      <c r="G9" s="17" t="inlineStr">
         <is>
           <t>6 нед, 30 чд</t>
         </is>
@@ -1210,7 +1207,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="11" t="n"/>
       <c r="K13" s="11" t="n"/>
-      <c r="L13" s="11" t="n"/>
+      <c r="L13" s="12" t="n"/>
       <c r="M13" s="11" t="n"/>
       <c r="N13" s="11" t="n"/>
       <c r="O13" s="11" t="n"/>
@@ -1240,7 +1237,7 @@
       <c r="I14" s="11" t="n"/>
       <c r="J14" s="11" t="n"/>
       <c r="K14" s="11" t="n"/>
-      <c r="L14" s="11" t="n"/>
+      <c r="L14" s="12" t="n"/>
       <c r="M14" s="11" t="n"/>
       <c r="N14" s="11" t="n"/>
       <c r="O14" s="11" t="n"/>
@@ -1261,7 +1258,7 @@
       <c r="D15" s="11" t="n"/>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="11" t="n"/>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="17" t="inlineStr">
         <is>
           <t>6 нед, 30 чд</t>
         </is>
@@ -1281,70 +1278,70 @@
       <c r="T15" s="12" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Легенда:</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="21" t="inlineStr">
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>◆ выполнено / факт</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="21" t="inlineStr">
         <is>
           <t>◇ план / под вопросом</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>работы (разработка)</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="24" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>аналитика (SDD)</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>тестирование</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="26" t="inlineStr">
+      <c r="B24" s="25" t="inlineStr">
         <is>
           <t>оценка т/з</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="27" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>отпуск</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="28" t="inlineStr">
+      <c r="B26" s="27" t="inlineStr">
         <is>
           <t>⚑ старт</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="29" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>⚑ финиш</t>
         </is>
